--- a/data/trans_orig/IP22D4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D4_2023-Edad-trans_orig.xlsx
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>21588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37032</t>
+          <t>36660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47786</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>52863</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94100</t>
+          <t>94306</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>100353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D4_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6261</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9752</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8014</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7473</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5042</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6487</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4477</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7028</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>63,7%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>11622</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9213</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12537</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>73,49%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19096</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>839</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,74 +1632,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8669</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5193</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>54,62%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9256</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6541</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>64,57%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>31</t>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21588</t>
+          <t>19430</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1745,107 +1745,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4314</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3589</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>35,43%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4638</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16678</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13264</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>95,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>19721</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>16906</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>12848</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17756</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,27 +2163,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36660</t>
+          <t>33007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4908</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4255</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4694</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,102 +2549,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>41616</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>37864</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>51507</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>47283</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>52863</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>88504</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>84107</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>90584</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>96,69%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>98249</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>94306</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>100353</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -2770,107 +2770,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
